--- a/output/laminas_comunales/comunal_s_isapre_a_2021_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2021_valparaiso.xlsx
@@ -375,436 +375,436 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Concón</t>
         </is>
       </c>
       <c r="C2">
-        <v>63980</v>
+        <v>33.00378139721571</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="C3">
-        <v>33154</v>
+        <v>21.64154652686763</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="C4">
-        <v>24638</v>
+        <v>21.33172517052071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
+          <t>Viña del Mar</t>
         </is>
       </c>
       <c r="C5">
-        <v>16864</v>
+        <v>19.08449317814381</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Concón</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="C6">
-        <v>15623</v>
+        <v>15.98207193918076</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Rinconada</t>
         </is>
       </c>
       <c r="C7">
-        <v>10150</v>
+        <v>15.19566638647614</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="C8">
-        <v>9856</v>
+        <v>15.18029403406966</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="C9">
-        <v>7718</v>
+        <v>15.03389613321699</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Villa Alemana</t>
         </is>
       </c>
       <c r="C10">
-        <v>7270</v>
+        <v>13.24432576769025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>San Esteban</t>
         </is>
       </c>
       <c r="C11">
-        <v>5129</v>
+        <v>12.74561311337606</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>Calle Larga</t>
         </is>
       </c>
       <c r="C12">
-        <v>5114</v>
+        <v>11.69076462159698</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="C13">
-        <v>3270</v>
+        <v>10.94695207073057</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="C14">
-        <v>2817</v>
+        <v>10.78164836880171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="C15">
-        <v>2642</v>
+        <v>10.38523139172216</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Nogales</t>
         </is>
       </c>
       <c r="C16">
-        <v>2548</v>
+        <v>10.04397231050546</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="C17">
-        <v>2469</v>
+        <v>9.896195865992798</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>San Esteban</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="C18">
-        <v>2426</v>
+        <v>9.826112018445576</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nogales</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="C19">
-        <v>2307</v>
+        <v>9.564172150141889</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="C20">
-        <v>1938</v>
+        <v>9.219277601555305</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="C21">
-        <v>1802</v>
+        <v>9.129451667608819</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="C22">
-        <v>1795</v>
+        <v>8.778336663680838</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rinconada</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="C23">
-        <v>1627</v>
+        <v>8.407605466428995</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="C24">
-        <v>1579</v>
+        <v>8.300279981334578</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="C25">
-        <v>1423</v>
+        <v>8.225672015003125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="C26">
-        <v>1361</v>
+        <v>7.532507900326374</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="C27">
-        <v>1263</v>
+        <v>6.593672787171164</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="C28">
-        <v>1108</v>
+        <v>6.189986712462707</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="C29">
-        <v>941</v>
+        <v>5.962609763006326</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="C30">
-        <v>879</v>
+        <v>5.913978494623656</v>
       </c>
     </row>
     <row r="31">
@@ -819,52 +819,52 @@
         </is>
       </c>
       <c r="C31">
-        <v>786</v>
+        <v>5.299710066752073</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="C32">
-        <v>724</v>
+        <v>4.969189892023292</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Santa María</t>
         </is>
       </c>
       <c r="C33">
-        <v>566</v>
+        <v>4.920483892891125</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="C34">
-        <v>451</v>
+        <v>4.33489827856025</v>
       </c>
     </row>
     <row r="35">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>359</v>
+        <v>3.618222132634549</v>
       </c>
     </row>
     <row r="36">
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>258</v>
+        <v>3.233487905752601</v>
       </c>
     </row>
     <row r="37">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>1.112347052280311</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +965,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
